--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_2/epoch_140/per_file_predictions_epoch_140.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_2/epoch_140/per_file_predictions_epoch_140.xlsx
@@ -892,7 +892,7 @@
     <t>0.0002,0.9997,0.0011,0.0000</t>
   </si>
   <si>
-    <t>0.2479,0.0023,0.8164,0.0012</t>
+    <t>0.2480,0.0023,0.8164,0.0012</t>
   </si>
   <si>
     <t>0.1068,0.0062,0.9132,0.0019</t>
@@ -1339,7 +1339,7 @@
     <t>0.7689,0.2524,0.0132,0.0077</t>
   </si>
   <si>
-    <t>0.4317,0.6382,0.0112,0.0054</t>
+    <t>0.4317,0.6381,0.0112,0.0054</t>
   </si>
   <si>
     <t>0.8914,0.1120,0.0044,0.0013</t>
@@ -1435,7 +1435,7 @@
     <t>0.5876,0.0240,0.3473,0.0085</t>
   </si>
   <si>
-    <t>0.1964,0.0005,0.8504,0.0020</t>
+    <t>0.1965,0.0005,0.8504,0.0020</t>
   </si>
   <si>
     <t>0.7317,0.0059,0.1878,0.0027</t>

--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_2/epoch_140/per_file_predictions_epoch_140.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_2/epoch_140/per_file_predictions_epoch_140.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="526">
   <si>
     <t>Filename</t>
   </si>
@@ -826,6 +826,15 @@
     <t>0,1,0,1</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0.9568,0.0021,0.0110,0.0023</t>
   </si>
   <si>
@@ -835,7 +844,7 @@
     <t>0.9684,0.0025,0.0016,0.0090</t>
   </si>
   <si>
-    <t>0.4046,0.0005,0.0013,0.6394</t>
+    <t>0.4038,0.0005,0.0012,0.6407</t>
   </si>
   <si>
     <t>0.9937,0.0021,0.0009,0.0002</t>
@@ -853,28 +862,28 @@
     <t>0.9612,0.0376,0.0005,0.0002</t>
   </si>
   <si>
-    <t>0.9813,0.0167,0.0018,0.0009</t>
-  </si>
-  <si>
-    <t>0.9907,0.0027,0.0017,0.0002</t>
-  </si>
-  <si>
-    <t>0.9903,0.0032,0.0020,0.0002</t>
-  </si>
-  <si>
-    <t>0.8152,0.0170,0.1452,0.0022</t>
-  </si>
-  <si>
-    <t>0.0164,0.0540,0.9460,0.0018</t>
-  </si>
-  <si>
-    <t>0.1107,0.0003,0.9461,0.0001</t>
+    <t>0.9814,0.0167,0.0018,0.0009</t>
+  </si>
+  <si>
+    <t>0.9908,0.0027,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.9904,0.0032,0.0020,0.0002</t>
+  </si>
+  <si>
+    <t>0.8156,0.0170,0.1447,0.0022</t>
+  </si>
+  <si>
+    <t>0.0164,0.0542,0.9457,0.0018</t>
+  </si>
+  <si>
+    <t>0.1107,0.0003,0.9460,0.0001</t>
   </si>
   <si>
     <t>0.0607,0.0035,0.9573,0.0010</t>
   </si>
   <si>
-    <t>0.8537,0.0006,0.1724,0.0001</t>
+    <t>0.8541,0.0006,0.1717,0.0001</t>
   </si>
   <si>
     <t>0.0004,0.9993,0.0008,0.0002</t>
@@ -883,73 +892,73 @@
     <t>0.0023,0.9967,0.0008,0.0008</t>
   </si>
   <si>
-    <t>0.0457,0.9773,0.0255,0.0001</t>
-  </si>
-  <si>
-    <t>0.0038,0.9937,0.0012,0.0024</t>
+    <t>0.0457,0.9773,0.0254,0.0001</t>
+  </si>
+  <si>
+    <t>0.0039,0.9937,0.0012,0.0024</t>
   </si>
   <si>
     <t>0.0002,0.9997,0.0011,0.0000</t>
   </si>
   <si>
-    <t>0.2480,0.0023,0.8164,0.0012</t>
-  </si>
-  <si>
-    <t>0.1068,0.0062,0.9132,0.0019</t>
+    <t>0.2486,0.0023,0.8159,0.0012</t>
+  </si>
+  <si>
+    <t>0.1070,0.0062,0.9129,0.0019</t>
   </si>
   <si>
     <t>0.0296,0.0001,0.9887,0.0000</t>
   </si>
   <si>
-    <t>0.0226,0.0019,0.9833,0.0008</t>
+    <t>0.0227,0.0019,0.9833,0.0008</t>
   </si>
   <si>
     <t>0.0158,0.0010,0.9907,0.0004</t>
   </si>
   <si>
-    <t>0.0378,0.0002,0.9781,0.0003</t>
+    <t>0.0378,0.0002,0.9780,0.0003</t>
   </si>
   <si>
     <t>0.0087,0.0003,0.9917,0.0010</t>
   </si>
   <si>
-    <t>0.6842,0.2609,0.0568,0.0021</t>
-  </si>
-  <si>
-    <t>0.8716,0.1349,0.0132,0.0007</t>
+    <t>0.6849,0.2610,0.0564,0.0021</t>
+  </si>
+  <si>
+    <t>0.8718,0.1351,0.0132,0.0007</t>
   </si>
   <si>
     <t>0.0026,0.0002,0.9981,0.0002</t>
   </si>
   <si>
-    <t>0.0057,0.5956,0.8383,0.0016</t>
-  </si>
-  <si>
-    <t>0.9473,0.0051,0.0248,0.0005</t>
-  </si>
-  <si>
-    <t>0.9206,0.0139,0.0399,0.0004</t>
-  </si>
-  <si>
-    <t>0.2227,0.8383,0.0341,0.0016</t>
-  </si>
-  <si>
-    <t>0.0060,0.9578,0.7470,0.0005</t>
-  </si>
-  <si>
-    <t>0.0023,0.8855,0.9249,0.0006</t>
+    <t>0.0057,0.5962,0.8378,0.0016</t>
+  </si>
+  <si>
+    <t>0.9474,0.0051,0.0247,0.0005</t>
+  </si>
+  <si>
+    <t>0.9209,0.0139,0.0397,0.0004</t>
+  </si>
+  <si>
+    <t>0.2228,0.8383,0.0340,0.0016</t>
+  </si>
+  <si>
+    <t>0.0060,0.9579,0.7462,0.0005</t>
+  </si>
+  <si>
+    <t>0.0023,0.8856,0.9247,0.0006</t>
   </si>
   <si>
     <t>0.0017,0.0006,0.9972,0.0005</t>
   </si>
   <si>
-    <t>0.0114,0.0201,0.9726,0.0023</t>
-  </si>
-  <si>
-    <t>0.2238,0.0002,0.7818,0.0034</t>
-  </si>
-  <si>
-    <t>0.0023,0.3066,0.9790,0.0006</t>
+    <t>0.0115,0.0200,0.9726,0.0023</t>
+  </si>
+  <si>
+    <t>0.2241,0.0002,0.7813,0.0034</t>
+  </si>
+  <si>
+    <t>0.0023,0.3067,0.9790,0.0006</t>
   </si>
   <si>
     <t>0.0006,0.9962,0.0080,0.0033</t>
@@ -958,22 +967,22 @@
     <t>0.0032,0.0106,0.9925,0.0011</t>
   </si>
   <si>
-    <t>0.0045,0.8668,0.0010,0.6847</t>
+    <t>0.0045,0.8668,0.0010,0.6842</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0006,0.0001</t>
   </si>
   <si>
-    <t>0.0001,0.9997,0.1422,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0184,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0738,0.9937,0.0004</t>
-  </si>
-  <si>
-    <t>0.0010,0.0568,0.9956,0.0003</t>
+    <t>0.0001,0.9997,0.1415,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0183,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0737,0.9937,0.0004</t>
+  </si>
+  <si>
+    <t>0.0010,0.0566,0.9956,0.0003</t>
   </si>
   <si>
     <t>0.0157,0.0016,0.9846,0.0019</t>
@@ -985,34 +994,34 @@
     <t>0.0068,0.0005,0.9950,0.0003</t>
   </si>
   <si>
-    <t>0.0366,0.0089,0.9513,0.0018</t>
-  </si>
-  <si>
-    <t>0.9564,0.0187,0.0183,0.0004</t>
-  </si>
-  <si>
-    <t>0.9661,0.0018,0.0212,0.0002</t>
-  </si>
-  <si>
-    <t>0.9796,0.0040,0.0065,0.0010</t>
-  </si>
-  <si>
-    <t>0.5749,0.0011,0.5317,0.0002</t>
+    <t>0.0367,0.0089,0.9512,0.0018</t>
+  </si>
+  <si>
+    <t>0.9565,0.0187,0.0182,0.0004</t>
+  </si>
+  <si>
+    <t>0.9663,0.0018,0.0211,0.0002</t>
+  </si>
+  <si>
+    <t>0.9797,0.0040,0.0065,0.0010</t>
+  </si>
+  <si>
+    <t>0.5756,0.0011,0.5307,0.0002</t>
   </si>
   <si>
     <t>0.9821,0.0014,0.0093,0.0002</t>
   </si>
   <si>
-    <t>0.9845,0.0038,0.0067,0.0004</t>
+    <t>0.9846,0.0038,0.0067,0.0004</t>
   </si>
   <si>
     <t>0.9921,0.0012,0.0029,0.0001</t>
   </si>
   <si>
-    <t>0.0001,0.9982,0.9277,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0419,0.9982,0.0001</t>
+    <t>0.0001,0.9982,0.9275,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0418,0.9982,0.0001</t>
   </si>
   <si>
     <t>0.0033,0.0039,0.9950,0.0008</t>
@@ -1030,10 +1039,10 @@
     <t>0.0000,0.9999,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9737,0.0013,0.0220,0.0001</t>
-  </si>
-  <si>
-    <t>0.2140,0.0541,0.7391,0.0073</t>
+    <t>0.9738,0.0013,0.0219,0.0001</t>
+  </si>
+  <si>
+    <t>0.2147,0.0541,0.7382,0.0073</t>
   </si>
   <si>
     <t>0.0092,0.0037,0.9915,0.0012</t>
@@ -1045,13 +1054,13 @@
     <t>0.0002,0.9697,0.9892,0.0000</t>
   </si>
   <si>
-    <t>0.0000,0.9999,0.0400,0.0000</t>
+    <t>0.0000,0.9999,0.0398,0.0000</t>
   </si>
   <si>
     <t>0.0003,0.9924,0.8752,0.0002</t>
   </si>
   <si>
-    <t>0.0208,0.0103,0.0019,0.9747</t>
+    <t>0.0208,0.0103,0.0018,0.9747</t>
   </si>
   <si>
     <t>0.0004,0.0006,0.0001,0.9999</t>
@@ -1063,19 +1072,19 @@
     <t>0.0037,0.0011,0.0016,0.9992</t>
   </si>
   <si>
-    <t>0.0407,0.0051,0.0019,0.9726</t>
+    <t>0.0406,0.0051,0.0019,0.9726</t>
   </si>
   <si>
     <t>0.0003,0.0018,0.0012,0.9999</t>
   </si>
   <si>
-    <t>0.0001,0.9971,0.9596,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.5676,0.9932,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.9609,0.6425,0.0010</t>
+    <t>0.0001,0.9971,0.9595,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.5671,0.9932,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.9609,0.6416,0.0010</t>
   </si>
   <si>
     <t>0.0005,0.9452,0.9814,0.0002</t>
@@ -1084,28 +1093,28 @@
     <t>0.0001,0.9945,0.9806,0.0000</t>
   </si>
   <si>
-    <t>0.0003,0.9941,0.8699,0.0001</t>
+    <t>0.0003,0.9942,0.8693,0.0001</t>
   </si>
   <si>
     <t>0.9931,0.0047,0.0005,0.0002</t>
   </si>
   <si>
-    <t>0.9660,0.0354,0.0046,0.0008</t>
-  </si>
-  <si>
-    <t>0.9326,0.0654,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.9851,0.0158,0.0018,0.0008</t>
-  </si>
-  <si>
-    <t>0.9859,0.0085,0.0031,0.0003</t>
+    <t>0.9662,0.0353,0.0046,0.0008</t>
+  </si>
+  <si>
+    <t>0.9326,0.0654,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9852,0.0158,0.0018,0.0008</t>
+  </si>
+  <si>
+    <t>0.9859,0.0084,0.0031,0.0003</t>
   </si>
   <si>
     <t>0.9915,0.0030,0.0007,0.0004</t>
   </si>
   <si>
-    <t>0.9855,0.0032,0.0058,0.0004</t>
+    <t>0.9856,0.0031,0.0058,0.0004</t>
   </si>
   <si>
     <t>0.9919,0.0024,0.0011,0.0004</t>
@@ -1132,19 +1141,19 @@
     <t>0.9935,0.0030,0.0007,0.0004</t>
   </si>
   <si>
-    <t>0.9905,0.0038,0.0017,0.0003</t>
+    <t>0.9906,0.0038,0.0017,0.0003</t>
   </si>
   <si>
     <t>0.0011,0.0001,0.9990,0.0001</t>
   </si>
   <si>
-    <t>0.0999,0.0008,0.9444,0.0004</t>
-  </si>
-  <si>
-    <t>0.9468,0.0003,0.0845,0.0000</t>
-  </si>
-  <si>
-    <t>0.0672,0.0010,0.9566,0.0004</t>
+    <t>0.1001,0.0008,0.9442,0.0004</t>
+  </si>
+  <si>
+    <t>0.9468,0.0003,0.0843,0.0000</t>
+  </si>
+  <si>
+    <t>0.0674,0.0010,0.9565,0.0004</t>
   </si>
   <si>
     <t>0.0002,0.9996,0.0001,0.0001</t>
@@ -1153,31 +1162,31 @@
     <t>0.0001,0.9999,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.5281,0.6246,0.0019,0.0003</t>
-  </si>
-  <si>
-    <t>0.0781,0.9332,0.0218,0.0016</t>
+    <t>0.5282,0.6244,0.0018,0.0003</t>
+  </si>
+  <si>
+    <t>0.0784,0.9331,0.0217,0.0016</t>
   </si>
   <si>
     <t>0.0003,0.9996,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.6465,0.4262,0.0338,0.0021</t>
-  </si>
-  <si>
-    <t>0.1700,0.0158,0.8338,0.0038</t>
-  </si>
-  <si>
-    <t>0.0413,0.0020,0.9663,0.0013</t>
-  </si>
-  <si>
-    <t>0.4867,0.0151,0.4958,0.0039</t>
-  </si>
-  <si>
-    <t>0.1462,0.0128,0.8628,0.0049</t>
-  </si>
-  <si>
-    <t>0.0017,0.6100,0.7284,0.0284</t>
+    <t>0.6477,0.4256,0.0335,0.0021</t>
+  </si>
+  <si>
+    <t>0.1707,0.0159,0.8330,0.0038</t>
+  </si>
+  <si>
+    <t>0.0414,0.0020,0.9663,0.0013</t>
+  </si>
+  <si>
+    <t>0.4875,0.0152,0.4946,0.0039</t>
+  </si>
+  <si>
+    <t>0.1465,0.0128,0.8625,0.0049</t>
+  </si>
+  <si>
+    <t>0.0017,0.6100,0.7279,0.0284</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0081,0.0000</t>
@@ -1189,46 +1198,46 @@
     <t>0.0002,0.9993,0.0004,0.0015</t>
   </si>
   <si>
-    <t>0.0000,0.9994,0.0748,0.0004</t>
-  </si>
-  <si>
-    <t>0.0027,0.9935,0.1715,0.0005</t>
-  </si>
-  <si>
-    <t>0.6482,0.2944,0.0566,0.0010</t>
-  </si>
-  <si>
-    <t>0.3881,0.6194,0.0613,0.0046</t>
-  </si>
-  <si>
-    <t>0.9938,0.0005,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.9736,0.0184,0.0008,0.0007</t>
+    <t>0.0000,0.9994,0.0745,0.0004</t>
+  </si>
+  <si>
+    <t>0.0028,0.9935,0.1708,0.0005</t>
+  </si>
+  <si>
+    <t>0.6491,0.2942,0.0563,0.0010</t>
+  </si>
+  <si>
+    <t>0.3886,0.6194,0.0610,0.0046</t>
+  </si>
+  <si>
+    <t>0.9938,0.0005,0.0025,0.0001</t>
+  </si>
+  <si>
+    <t>0.9736,0.0185,0.0008,0.0007</t>
   </si>
   <si>
     <t>0.9871,0.0061,0.0018,0.0005</t>
   </si>
   <si>
-    <t>0.9843,0.0027,0.0063,0.0003</t>
+    <t>0.9844,0.0027,0.0063,0.0003</t>
   </si>
   <si>
     <t>0.9955,0.0019,0.0005,0.0001</t>
   </si>
   <si>
-    <t>0.9764,0.0012,0.0100,0.0003</t>
+    <t>0.9764,0.0012,0.0099,0.0003</t>
   </si>
   <si>
     <t>0.9893,0.0022,0.0027,0.0003</t>
   </si>
   <si>
-    <t>0.9931,0.0013,0.0018,0.0002</t>
-  </si>
-  <si>
-    <t>0.0020,0.9427,0.9213,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.5979,0.9972,0.0000</t>
+    <t>0.9931,0.0013,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.0020,0.9428,0.9212,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.5974,0.9972,0.0000</t>
   </si>
   <si>
     <t>0.0003,0.0038,0.9985,0.0011</t>
@@ -1237,16 +1246,16 @@
     <t>0.0050,0.0189,0.9935,0.0002</t>
   </si>
   <si>
-    <t>0.9518,0.0027,0.0399,0.0002</t>
-  </si>
-  <si>
-    <t>0.5022,0.2594,0.0760,0.0073</t>
-  </si>
-  <si>
-    <t>0.1068,0.0001,0.9319,0.0007</t>
-  </si>
-  <si>
-    <t>0.7983,0.0127,0.1650,0.0021</t>
+    <t>0.9519,0.0027,0.0398,0.0002</t>
+  </si>
+  <si>
+    <t>0.5026,0.2601,0.0755,0.0073</t>
+  </si>
+  <si>
+    <t>0.1068,0.0001,0.9318,0.0007</t>
+  </si>
+  <si>
+    <t>0.7989,0.0127,0.1642,0.0020</t>
   </si>
   <si>
     <t>0.0209,0.0003,0.0021,0.9956</t>
@@ -1261,55 +1270,55 @@
     <t>0.0079,0.0002,0.0007,0.9987</t>
   </si>
   <si>
-    <t>0.0001,0.9963,0.9678,0.0000</t>
-  </si>
-  <si>
-    <t>0.9805,0.0010,0.0086,0.0004</t>
+    <t>0.0001,0.9963,0.9677,0.0000</t>
+  </si>
+  <si>
+    <t>0.9806,0.0010,0.0086,0.0004</t>
   </si>
   <si>
     <t>0.0106,0.9820,0.0054,0.0071</t>
   </si>
   <si>
-    <t>0.9932,0.0007,0.0025,0.0001</t>
-  </si>
-  <si>
-    <t>0.0275,0.9734,0.0054,0.0016</t>
+    <t>0.9932,0.0007,0.0024,0.0001</t>
+  </si>
+  <si>
+    <t>0.0276,0.9733,0.0053,0.0016</t>
   </si>
   <si>
     <t>0.9949,0.0006,0.0007,0.0003</t>
   </si>
   <si>
-    <t>0.5536,0.0000,0.5175,0.0000</t>
-  </si>
-  <si>
-    <t>0.7719,0.0000,0.2575,0.0001</t>
+    <t>0.5546,0.0000,0.5162,0.0000</t>
+  </si>
+  <si>
+    <t>0.7727,0.0000,0.2564,0.0001</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9677,0.0001,0.0153,0.0002</t>
+    <t>0.9678,0.0001,0.0152,0.0002</t>
   </si>
   <si>
     <t>0.9886,0.0019,0.0019,0.0001</t>
   </si>
   <si>
-    <t>0.8589,0.0671,0.0233,0.0005</t>
+    <t>0.8589,0.0673,0.0233,0.0005</t>
   </si>
   <si>
     <t>0.9862,0.0014,0.0060,0.0002</t>
   </si>
   <si>
-    <t>0.9066,0.0416,0.0368,0.0020</t>
-  </si>
-  <si>
-    <t>0.0782,0.8905,0.0196,0.0198</t>
-  </si>
-  <si>
-    <t>0.9224,0.0381,0.0263,0.0008</t>
-  </si>
-  <si>
-    <t>0.9445,0.0126,0.0303,0.0008</t>
+    <t>0.9067,0.0417,0.0367,0.0020</t>
+  </si>
+  <si>
+    <t>0.0781,0.8906,0.0196,0.0198</t>
+  </si>
+  <si>
+    <t>0.9226,0.0382,0.0261,0.0008</t>
+  </si>
+  <si>
+    <t>0.9446,0.0126,0.0302,0.0008</t>
   </si>
   <si>
     <t>0.9896,0.0067,0.0012,0.0002</t>
@@ -1336,46 +1345,46 @@
     <t>0.9923,0.0020,0.0013,0.0002</t>
   </si>
   <si>
-    <t>0.7689,0.2524,0.0132,0.0077</t>
-  </si>
-  <si>
-    <t>0.4317,0.6381,0.0112,0.0054</t>
-  </si>
-  <si>
-    <t>0.8914,0.1120,0.0044,0.0013</t>
-  </si>
-  <si>
-    <t>0.8057,0.0068,0.1807,0.0004</t>
-  </si>
-  <si>
-    <t>0.9794,0.0073,0.0063,0.0005</t>
-  </si>
-  <si>
-    <t>0.9365,0.0168,0.0272,0.0007</t>
-  </si>
-  <si>
-    <t>0.9784,0.0053,0.0079,0.0003</t>
-  </si>
-  <si>
-    <t>0.9026,0.0750,0.0302,0.0048</t>
+    <t>0.7692,0.2521,0.0131,0.0077</t>
+  </si>
+  <si>
+    <t>0.4316,0.6381,0.0111,0.0054</t>
+  </si>
+  <si>
+    <t>0.8915,0.1118,0.0044,0.0013</t>
+  </si>
+  <si>
+    <t>0.8069,0.0068,0.1793,0.0004</t>
+  </si>
+  <si>
+    <t>0.9795,0.0073,0.0063,0.0005</t>
+  </si>
+  <si>
+    <t>0.9367,0.0168,0.0271,0.0007</t>
+  </si>
+  <si>
+    <t>0.9785,0.0053,0.0078,0.0003</t>
+  </si>
+  <si>
+    <t>0.9029,0.0749,0.0301,0.0048</t>
   </si>
   <si>
     <t>0.0045,0.0027,0.9972,0.0001</t>
   </si>
   <si>
-    <t>0.9525,0.0129,0.0225,0.0003</t>
+    <t>0.9527,0.0128,0.0223,0.0003</t>
   </si>
   <si>
     <t>0.0008,0.0002,0.9994,0.0000</t>
   </si>
   <si>
-    <t>0.0006,0.0959,0.9861,0.0033</t>
+    <t>0.0006,0.0957,0.9861,0.0033</t>
   </si>
   <si>
     <t>0.0097,0.0013,0.9922,0.0010</t>
   </si>
   <si>
-    <t>0.0041,0.6211,0.8986,0.0006</t>
+    <t>0.0041,0.6217,0.8982,0.0006</t>
   </si>
   <si>
     <t>0.0040,0.0008,0.9974,0.0001</t>
@@ -1384,76 +1393,76 @@
     <t>0.0013,0.0000,0.9994,0.0000</t>
   </si>
   <si>
-    <t>0.0129,0.0003,0.9924,0.0003</t>
+    <t>0.0130,0.0003,0.9924,0.0003</t>
   </si>
   <si>
     <t>0.0933,0.0019,0.9320,0.0015</t>
   </si>
   <si>
-    <t>0.1307,0.0029,0.8851,0.0018</t>
-  </si>
-  <si>
-    <t>0.6768,0.0718,0.1996,0.0066</t>
-  </si>
-  <si>
-    <t>0.0316,0.0084,0.9644,0.0033</t>
-  </si>
-  <si>
-    <t>0.0123,0.0567,0.9632,0.0006</t>
+    <t>0.1310,0.0029,0.8847,0.0018</t>
+  </si>
+  <si>
+    <t>0.6773,0.0719,0.1988,0.0066</t>
+  </si>
+  <si>
+    <t>0.0317,0.0084,0.9643,0.0033</t>
+  </si>
+  <si>
+    <t>0.0124,0.0569,0.9630,0.0006</t>
   </si>
   <si>
     <t>0.0690,0.0027,0.9379,0.0024</t>
   </si>
   <si>
-    <t>0.1809,0.0050,0.8320,0.0036</t>
-  </si>
-  <si>
-    <t>0.5117,0.0116,0.4964,0.0018</t>
-  </si>
-  <si>
-    <t>0.2128,0.8784,0.0032,0.0001</t>
+    <t>0.1812,0.0051,0.8317,0.0036</t>
+  </si>
+  <si>
+    <t>0.5124,0.0117,0.4954,0.0018</t>
+  </si>
+  <si>
+    <t>0.2130,0.8783,0.0031,0.0001</t>
   </si>
   <si>
     <t>0.0020,0.9976,0.0013,0.0002</t>
   </si>
   <si>
-    <t>0.0623,0.9592,0.0020,0.0005</t>
-  </si>
-  <si>
-    <t>0.9623,0.0308,0.0072,0.0005</t>
-  </si>
-  <si>
-    <t>0.4947,0.5815,0.0117,0.0018</t>
-  </si>
-  <si>
-    <t>0.3073,0.6842,0.0155,0.0012</t>
-  </si>
-  <si>
-    <t>0.9475,0.0031,0.0336,0.0003</t>
-  </si>
-  <si>
-    <t>0.5876,0.0240,0.3473,0.0085</t>
-  </si>
-  <si>
-    <t>0.1965,0.0005,0.8504,0.0020</t>
-  </si>
-  <si>
-    <t>0.7317,0.0059,0.1878,0.0027</t>
+    <t>0.0625,0.9591,0.0020,0.0005</t>
+  </si>
+  <si>
+    <t>0.9624,0.0307,0.0071,0.0005</t>
+  </si>
+  <si>
+    <t>0.4959,0.5809,0.0116,0.0018</t>
+  </si>
+  <si>
+    <t>0.3071,0.6847,0.0154,0.0012</t>
+  </si>
+  <si>
+    <t>0.9477,0.0031,0.0334,0.0003</t>
+  </si>
+  <si>
+    <t>0.5881,0.0240,0.3466,0.0085</t>
+  </si>
+  <si>
+    <t>0.1961,0.0005,0.8506,0.0020</t>
+  </si>
+  <si>
+    <t>0.7325,0.0059,0.1869,0.0027</t>
   </si>
   <si>
     <t>0.0061,0.0005,0.9944,0.0009</t>
   </si>
   <si>
-    <t>0.0410,0.0036,0.9722,0.0010</t>
-  </si>
-  <si>
-    <t>0.0438,0.0150,0.9558,0.0005</t>
+    <t>0.0412,0.0036,0.9720,0.0010</t>
+  </si>
+  <si>
+    <t>0.0439,0.0150,0.9557,0.0005</t>
   </si>
   <si>
     <t>0.0066,0.0031,0.9919,0.0005</t>
   </si>
   <si>
-    <t>0.0784,0.0032,0.9276,0.0001</t>
+    <t>0.0786,0.0032,0.9273,0.0001</t>
   </si>
   <si>
     <t>0.9935,0.0009,0.0018,0.0001</t>
@@ -1462,31 +1471,31 @@
     <t>0.9682,0.0342,0.0053,0.0008</t>
   </si>
   <si>
-    <t>0.9601,0.0247,0.0078,0.0025</t>
+    <t>0.9602,0.0247,0.0077,0.0025</t>
   </si>
   <si>
     <t>0.9789,0.0150,0.0010,0.0005</t>
   </si>
   <si>
-    <t>0.9299,0.0560,0.0163,0.0038</t>
-  </si>
-  <si>
-    <t>0.9586,0.0321,0.0067,0.0028</t>
-  </si>
-  <si>
-    <t>0.9785,0.0104,0.0041,0.0006</t>
+    <t>0.9302,0.0558,0.0162,0.0038</t>
+  </si>
+  <si>
+    <t>0.9587,0.0320,0.0067,0.0028</t>
+  </si>
+  <si>
+    <t>0.9786,0.0104,0.0041,0.0006</t>
   </si>
   <si>
     <t>0.9944,0.0010,0.0013,0.0001</t>
   </si>
   <si>
-    <t>0.0148,0.0006,0.9915,0.0002</t>
-  </si>
-  <si>
-    <t>0.1051,0.0160,0.9026,0.0024</t>
-  </si>
-  <si>
-    <t>0.5808,0.0097,0.3234,0.0108</t>
+    <t>0.0149,0.0006,0.9915,0.0002</t>
+  </si>
+  <si>
+    <t>0.1055,0.0160,0.9022,0.0024</t>
+  </si>
+  <si>
+    <t>0.5819,0.0097,0.3221,0.0108</t>
   </si>
   <si>
     <t>0.0005,0.0002,0.9995,0.0000</t>
@@ -1495,7 +1504,7 @@
     <t>0.0003,0.0016,0.9992,0.0003</t>
   </si>
   <si>
-    <t>0.0072,0.0173,0.9823,0.0008</t>
+    <t>0.0072,0.0173,0.9823,0.0009</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.9999,0.0000</t>
@@ -1510,58 +1519,58 @@
     <t>0.0344,0.0170,0.9452,0.0065</t>
   </si>
   <si>
-    <t>0.7372,0.0011,0.2799,0.0014</t>
-  </si>
-  <si>
-    <t>0.4280,0.0006,0.4913,0.0097</t>
-  </si>
-  <si>
-    <t>0.9348,0.0055,0.0426,0.0003</t>
-  </si>
-  <si>
-    <t>0.9917,0.0042,0.0012,0.0002</t>
+    <t>0.7373,0.0011,0.2795,0.0014</t>
+  </si>
+  <si>
+    <t>0.4284,0.0006,0.4906,0.0097</t>
+  </si>
+  <si>
+    <t>0.9348,0.0055,0.0425,0.0003</t>
+  </si>
+  <si>
+    <t>0.9917,0.0042,0.0011,0.0002</t>
   </si>
   <si>
     <t>0.9868,0.0104,0.0005,0.0003</t>
   </si>
   <si>
-    <t>0.9896,0.0082,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.9348,0.0593,0.0112,0.0015</t>
+    <t>0.9897,0.0082,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.9349,0.0592,0.0112,0.0015</t>
   </si>
   <si>
     <t>0.9936,0.0010,0.0018,0.0001</t>
   </si>
   <si>
-    <t>0.9804,0.0177,0.0026,0.0006</t>
-  </si>
-  <si>
-    <t>0.9882,0.0088,0.0017,0.0008</t>
-  </si>
-  <si>
-    <t>0.9873,0.0037,0.0028,0.0008</t>
-  </si>
-  <si>
-    <t>0.0031,0.2334,0.8844,0.0017</t>
-  </si>
-  <si>
-    <t>0.0018,0.0083,0.9979,0.0001</t>
-  </si>
-  <si>
-    <t>0.0020,0.0023,0.9981,0.0001</t>
-  </si>
-  <si>
-    <t>0.0217,0.0229,0.9420,0.0016</t>
+    <t>0.9805,0.0177,0.0026,0.0006</t>
+  </si>
+  <si>
+    <t>0.9883,0.0088,0.0017,0.0008</t>
+  </si>
+  <si>
+    <t>0.9873,0.0037,0.0027,0.0008</t>
+  </si>
+  <si>
+    <t>0.0031,0.2338,0.8842,0.0017</t>
+  </si>
+  <si>
+    <t>0.0018,0.0082,0.9979,0.0001</t>
+  </si>
+  <si>
+    <t>0.0020,0.0023,0.9981,0.0002</t>
+  </si>
+  <si>
+    <t>0.0217,0.0230,0.9417,0.0016</t>
   </si>
   <si>
     <t>0.0103,0.0003,0.9947,0.0001</t>
   </si>
   <si>
-    <t>0.1894,0.0155,0.1478,0.2444</t>
-  </si>
-  <si>
-    <t>0.1211,0.0095,0.8798,0.0051</t>
+    <t>0.1895,0.0155,0.1468,0.2455</t>
+  </si>
+  <si>
+    <t>0.1214,0.0095,0.8795,0.0051</t>
   </si>
   <si>
     <t>0.0015,0.0000,0.9970,0.0013</t>
@@ -1573,16 +1582,16 @@
     <t>0.0008,0.0139,0.0002,0.9997</t>
   </si>
   <si>
-    <t>0.0593,0.0008,0.0054,0.9848</t>
-  </si>
-  <si>
-    <t>0.0007,0.0002,0.0338,0.9994</t>
+    <t>0.0592,0.0008,0.0054,0.9848</t>
+  </si>
+  <si>
+    <t>0.0007,0.0002,0.0337,0.9994</t>
   </si>
   <si>
     <t>0.0002,0.0015,0.0009,0.9999</t>
   </si>
   <si>
-    <t>0.7983,0.0084,0.0135,0.1255</t>
+    <t>0.7982,0.0084,0.0134,0.1256</t>
   </si>
 </sst>
 </file>
@@ -1968,7 +1977,7 @@
         <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1982,7 +1991,7 @@
         <v>265</v>
       </c>
       <c r="D3" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1996,7 +2005,7 @@
         <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2010,7 +2019,7 @@
         <v>265</v>
       </c>
       <c r="D5" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2024,7 +2033,7 @@
         <v>264</v>
       </c>
       <c r="D6" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2038,7 +2047,7 @@
         <v>264</v>
       </c>
       <c r="D7" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2052,7 +2061,7 @@
         <v>264</v>
       </c>
       <c r="D8" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2066,7 +2075,7 @@
         <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2080,7 +2089,7 @@
         <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2094,7 +2103,7 @@
         <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2108,7 +2117,7 @@
         <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2122,7 +2131,7 @@
         <v>264</v>
       </c>
       <c r="D13" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2136,7 +2145,7 @@
         <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2150,7 +2159,7 @@
         <v>266</v>
       </c>
       <c r="D15" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2164,7 +2173,7 @@
         <v>266</v>
       </c>
       <c r="D16" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2178,7 +2187,7 @@
         <v>266</v>
       </c>
       <c r="D17" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2192,7 +2201,7 @@
         <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2206,7 +2215,7 @@
         <v>267</v>
       </c>
       <c r="D19" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2220,7 +2229,7 @@
         <v>267</v>
       </c>
       <c r="D20" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2234,7 +2243,7 @@
         <v>267</v>
       </c>
       <c r="D21" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2248,7 +2257,7 @@
         <v>267</v>
       </c>
       <c r="D22" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2262,7 +2271,7 @@
         <v>267</v>
       </c>
       <c r="D23" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2276,7 +2285,7 @@
         <v>266</v>
       </c>
       <c r="D24" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2290,7 +2299,7 @@
         <v>266</v>
       </c>
       <c r="D25" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2304,7 +2313,7 @@
         <v>266</v>
       </c>
       <c r="D26" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2318,7 +2327,7 @@
         <v>266</v>
       </c>
       <c r="D27" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2332,7 +2341,7 @@
         <v>266</v>
       </c>
       <c r="D28" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2346,7 +2355,7 @@
         <v>266</v>
       </c>
       <c r="D29" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2360,7 +2369,7 @@
         <v>266</v>
       </c>
       <c r="D30" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2374,7 +2383,7 @@
         <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2388,7 +2397,7 @@
         <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2402,7 +2411,7 @@
         <v>266</v>
       </c>
       <c r="D33" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2416,7 +2425,7 @@
         <v>268</v>
       </c>
       <c r="D34" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2430,7 +2439,7 @@
         <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2444,7 +2453,7 @@
         <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2458,7 +2467,7 @@
         <v>267</v>
       </c>
       <c r="D37" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2472,7 +2481,7 @@
         <v>268</v>
       </c>
       <c r="D38" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2486,7 +2495,7 @@
         <v>268</v>
       </c>
       <c r="D39" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2500,7 +2509,7 @@
         <v>266</v>
       </c>
       <c r="D40" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2514,7 +2523,7 @@
         <v>266</v>
       </c>
       <c r="D41" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2528,7 +2537,7 @@
         <v>266</v>
       </c>
       <c r="D42" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2542,7 +2551,7 @@
         <v>266</v>
       </c>
       <c r="D43" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2556,7 +2565,7 @@
         <v>267</v>
       </c>
       <c r="D44" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2570,7 +2579,7 @@
         <v>266</v>
       </c>
       <c r="D45" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2584,7 +2593,7 @@
         <v>269</v>
       </c>
       <c r="D46" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2598,7 +2607,7 @@
         <v>267</v>
       </c>
       <c r="D47" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2612,7 +2621,7 @@
         <v>267</v>
       </c>
       <c r="D48" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2626,7 +2635,7 @@
         <v>267</v>
       </c>
       <c r="D49" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2640,7 +2649,7 @@
         <v>266</v>
       </c>
       <c r="D50" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2654,7 +2663,7 @@
         <v>266</v>
       </c>
       <c r="D51" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2668,7 +2677,7 @@
         <v>266</v>
       </c>
       <c r="D52" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2682,7 +2691,7 @@
         <v>266</v>
       </c>
       <c r="D53" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2696,7 +2705,7 @@
         <v>266</v>
       </c>
       <c r="D54" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2710,7 +2719,7 @@
         <v>266</v>
       </c>
       <c r="D55" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2724,7 +2733,7 @@
         <v>264</v>
       </c>
       <c r="D56" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2738,7 +2747,7 @@
         <v>264</v>
       </c>
       <c r="D57" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2752,7 +2761,7 @@
         <v>264</v>
       </c>
       <c r="D58" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2763,10 +2772,10 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D59" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2780,7 +2789,7 @@
         <v>264</v>
       </c>
       <c r="D60" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2794,7 +2803,7 @@
         <v>264</v>
       </c>
       <c r="D61" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2808,7 +2817,7 @@
         <v>264</v>
       </c>
       <c r="D62" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2822,7 +2831,7 @@
         <v>268</v>
       </c>
       <c r="D63" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2836,7 +2845,7 @@
         <v>266</v>
       </c>
       <c r="D64" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2850,7 +2859,7 @@
         <v>266</v>
       </c>
       <c r="D65" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2864,7 +2873,7 @@
         <v>268</v>
       </c>
       <c r="D66" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2878,7 +2887,7 @@
         <v>266</v>
       </c>
       <c r="D67" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2892,7 +2901,7 @@
         <v>267</v>
       </c>
       <c r="D68" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2906,7 +2915,7 @@
         <v>267</v>
       </c>
       <c r="D69" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2920,7 +2929,7 @@
         <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2934,7 +2943,7 @@
         <v>266</v>
       </c>
       <c r="D71" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2948,7 +2957,7 @@
         <v>266</v>
       </c>
       <c r="D72" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2962,7 +2971,7 @@
         <v>268</v>
       </c>
       <c r="D73" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2976,7 +2985,7 @@
         <v>268</v>
       </c>
       <c r="D74" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2990,7 +2999,7 @@
         <v>267</v>
       </c>
       <c r="D75" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3004,7 +3013,7 @@
         <v>268</v>
       </c>
       <c r="D76" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3018,7 +3027,7 @@
         <v>265</v>
       </c>
       <c r="D77" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3032,7 +3041,7 @@
         <v>265</v>
       </c>
       <c r="D78" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3046,7 +3055,7 @@
         <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3060,7 +3069,7 @@
         <v>265</v>
       </c>
       <c r="D80" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3074,7 +3083,7 @@
         <v>265</v>
       </c>
       <c r="D81" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3088,7 +3097,7 @@
         <v>265</v>
       </c>
       <c r="D82" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3102,7 +3111,7 @@
         <v>268</v>
       </c>
       <c r="D83" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3116,7 +3125,7 @@
         <v>268</v>
       </c>
       <c r="D84" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3130,7 +3139,7 @@
         <v>268</v>
       </c>
       <c r="D85" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3144,7 +3153,7 @@
         <v>268</v>
       </c>
       <c r="D86" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3158,7 +3167,7 @@
         <v>268</v>
       </c>
       <c r="D87" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3172,7 +3181,7 @@
         <v>268</v>
       </c>
       <c r="D88" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3186,7 +3195,7 @@
         <v>264</v>
       </c>
       <c r="D89" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3200,7 +3209,7 @@
         <v>264</v>
       </c>
       <c r="D90" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3214,7 +3223,7 @@
         <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3228,7 +3237,7 @@
         <v>264</v>
       </c>
       <c r="D92" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3242,7 +3251,7 @@
         <v>264</v>
       </c>
       <c r="D93" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3256,7 +3265,7 @@
         <v>264</v>
       </c>
       <c r="D94" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3270,7 +3279,7 @@
         <v>264</v>
       </c>
       <c r="D95" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3284,7 +3293,7 @@
         <v>264</v>
       </c>
       <c r="D96" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3298,7 +3307,7 @@
         <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3312,7 +3321,7 @@
         <v>264</v>
       </c>
       <c r="D98" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3326,7 +3335,7 @@
         <v>264</v>
       </c>
       <c r="D99" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3340,7 +3349,7 @@
         <v>264</v>
       </c>
       <c r="D100" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3354,7 +3363,7 @@
         <v>264</v>
       </c>
       <c r="D101" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3368,7 +3377,7 @@
         <v>264</v>
       </c>
       <c r="D102" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3382,7 +3391,7 @@
         <v>264</v>
       </c>
       <c r="D103" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3396,7 +3405,7 @@
         <v>264</v>
       </c>
       <c r="D104" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3410,7 +3419,7 @@
         <v>266</v>
       </c>
       <c r="D105" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3424,7 +3433,7 @@
         <v>266</v>
       </c>
       <c r="D106" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3438,7 +3447,7 @@
         <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3452,7 +3461,7 @@
         <v>266</v>
       </c>
       <c r="D108" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3466,7 +3475,7 @@
         <v>267</v>
       </c>
       <c r="D109" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3480,7 +3489,7 @@
         <v>267</v>
       </c>
       <c r="D110" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3491,10 +3500,10 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D111" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3508,7 +3517,7 @@
         <v>267</v>
       </c>
       <c r="D112" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3522,7 +3531,7 @@
         <v>267</v>
       </c>
       <c r="D113" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3536,7 +3545,7 @@
         <v>267</v>
       </c>
       <c r="D114" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3550,7 +3559,7 @@
         <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3564,7 +3573,7 @@
         <v>266</v>
       </c>
       <c r="D116" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3578,7 +3587,7 @@
         <v>266</v>
       </c>
       <c r="D117" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3589,10 +3598,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D118" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3606,7 +3615,7 @@
         <v>266</v>
       </c>
       <c r="D119" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3620,7 +3629,7 @@
         <v>268</v>
       </c>
       <c r="D120" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3634,7 +3643,7 @@
         <v>267</v>
       </c>
       <c r="D121" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3648,7 +3657,7 @@
         <v>267</v>
       </c>
       <c r="D122" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3662,7 +3671,7 @@
         <v>267</v>
       </c>
       <c r="D123" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3676,7 +3685,7 @@
         <v>267</v>
       </c>
       <c r="D124" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3690,7 +3699,7 @@
         <v>267</v>
       </c>
       <c r="D125" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3704,7 +3713,7 @@
         <v>264</v>
       </c>
       <c r="D126" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3718,7 +3727,7 @@
         <v>267</v>
       </c>
       <c r="D127" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3732,7 +3741,7 @@
         <v>264</v>
       </c>
       <c r="D128" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3746,7 +3755,7 @@
         <v>264</v>
       </c>
       <c r="D129" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3760,7 +3769,7 @@
         <v>264</v>
       </c>
       <c r="D130" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3774,7 +3783,7 @@
         <v>264</v>
       </c>
       <c r="D131" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3788,7 +3797,7 @@
         <v>264</v>
       </c>
       <c r="D132" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3802,7 +3811,7 @@
         <v>264</v>
       </c>
       <c r="D133" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3816,7 +3825,7 @@
         <v>264</v>
       </c>
       <c r="D134" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3830,7 +3839,7 @@
         <v>264</v>
       </c>
       <c r="D135" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3844,7 +3853,7 @@
         <v>268</v>
       </c>
       <c r="D136" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3858,7 +3867,7 @@
         <v>268</v>
       </c>
       <c r="D137" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3872,7 +3881,7 @@
         <v>266</v>
       </c>
       <c r="D138" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3886,7 +3895,7 @@
         <v>266</v>
       </c>
       <c r="D139" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3900,7 +3909,7 @@
         <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3914,7 +3923,7 @@
         <v>264</v>
       </c>
       <c r="D141" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3928,7 +3937,7 @@
         <v>266</v>
       </c>
       <c r="D142" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3942,7 +3951,7 @@
         <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3956,7 +3965,7 @@
         <v>265</v>
       </c>
       <c r="D144" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3970,7 +3979,7 @@
         <v>265</v>
       </c>
       <c r="D145" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3984,7 +3993,7 @@
         <v>265</v>
       </c>
       <c r="D146" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3998,7 +4007,7 @@
         <v>265</v>
       </c>
       <c r="D147" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4012,7 +4021,7 @@
         <v>268</v>
       </c>
       <c r="D148" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4026,7 +4035,7 @@
         <v>264</v>
       </c>
       <c r="D149" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4040,7 +4049,7 @@
         <v>267</v>
       </c>
       <c r="D150" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4054,7 +4063,7 @@
         <v>264</v>
       </c>
       <c r="D151" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4068,7 +4077,7 @@
         <v>267</v>
       </c>
       <c r="D152" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4082,7 +4091,7 @@
         <v>264</v>
       </c>
       <c r="D153" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4093,10 +4102,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D154" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4110,7 +4119,7 @@
         <v>264</v>
       </c>
       <c r="D155" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4124,7 +4133,7 @@
         <v>266</v>
       </c>
       <c r="D156" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4138,7 +4147,7 @@
         <v>264</v>
       </c>
       <c r="D157" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4152,7 +4161,7 @@
         <v>264</v>
       </c>
       <c r="D158" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4166,7 +4175,7 @@
         <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4180,7 +4189,7 @@
         <v>264</v>
       </c>
       <c r="D160" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4194,7 +4203,7 @@
         <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4208,7 +4217,7 @@
         <v>267</v>
       </c>
       <c r="D162" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4222,7 +4231,7 @@
         <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4236,7 +4245,7 @@
         <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4250,7 +4259,7 @@
         <v>264</v>
       </c>
       <c r="D165" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4264,7 +4273,7 @@
         <v>264</v>
       </c>
       <c r="D166" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4278,7 +4287,7 @@
         <v>264</v>
       </c>
       <c r="D167" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4292,7 +4301,7 @@
         <v>264</v>
       </c>
       <c r="D168" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4306,7 +4315,7 @@
         <v>264</v>
       </c>
       <c r="D169" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4320,7 +4329,7 @@
         <v>264</v>
       </c>
       <c r="D170" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4334,7 +4343,7 @@
         <v>264</v>
       </c>
       <c r="D171" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4348,7 +4357,7 @@
         <v>264</v>
       </c>
       <c r="D172" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4362,7 +4371,7 @@
         <v>264</v>
       </c>
       <c r="D173" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4376,7 +4385,7 @@
         <v>267</v>
       </c>
       <c r="D174" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4390,7 +4399,7 @@
         <v>264</v>
       </c>
       <c r="D175" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4404,7 +4413,7 @@
         <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4418,7 +4427,7 @@
         <v>264</v>
       </c>
       <c r="D177" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4432,7 +4441,7 @@
         <v>264</v>
       </c>
       <c r="D178" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4446,7 +4455,7 @@
         <v>264</v>
       </c>
       <c r="D179" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4460,7 +4469,7 @@
         <v>264</v>
       </c>
       <c r="D180" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4474,7 +4483,7 @@
         <v>266</v>
       </c>
       <c r="D181" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4488,7 +4497,7 @@
         <v>264</v>
       </c>
       <c r="D182" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4502,7 +4511,7 @@
         <v>266</v>
       </c>
       <c r="D183" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4516,7 +4525,7 @@
         <v>266</v>
       </c>
       <c r="D184" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4530,7 +4539,7 @@
         <v>266</v>
       </c>
       <c r="D185" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4544,7 +4553,7 @@
         <v>268</v>
       </c>
       <c r="D186" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4558,7 +4567,7 @@
         <v>266</v>
       </c>
       <c r="D187" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4572,7 +4581,7 @@
         <v>266</v>
       </c>
       <c r="D188" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4586,7 +4595,7 @@
         <v>266</v>
       </c>
       <c r="D189" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4600,7 +4609,7 @@
         <v>266</v>
       </c>
       <c r="D190" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4614,7 +4623,7 @@
         <v>266</v>
       </c>
       <c r="D191" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4628,7 +4637,7 @@
         <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4642,7 +4651,7 @@
         <v>266</v>
       </c>
       <c r="D193" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4656,7 +4665,7 @@
         <v>266</v>
       </c>
       <c r="D194" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4670,7 +4679,7 @@
         <v>266</v>
       </c>
       <c r="D195" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4684,7 +4693,7 @@
         <v>266</v>
       </c>
       <c r="D196" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4698,7 +4707,7 @@
         <v>264</v>
       </c>
       <c r="D197" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4712,7 +4721,7 @@
         <v>267</v>
       </c>
       <c r="D198" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4726,7 +4735,7 @@
         <v>267</v>
       </c>
       <c r="D199" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4740,7 +4749,7 @@
         <v>267</v>
       </c>
       <c r="D200" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4754,7 +4763,7 @@
         <v>264</v>
       </c>
       <c r="D201" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4768,7 +4777,7 @@
         <v>267</v>
       </c>
       <c r="D202" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4782,7 +4791,7 @@
         <v>267</v>
       </c>
       <c r="D203" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4796,7 +4805,7 @@
         <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4810,7 +4819,7 @@
         <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4824,7 +4833,7 @@
         <v>266</v>
       </c>
       <c r="D206" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4838,7 +4847,7 @@
         <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4852,7 +4861,7 @@
         <v>266</v>
       </c>
       <c r="D208" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4866,7 +4875,7 @@
         <v>266</v>
       </c>
       <c r="D209" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4880,7 +4889,7 @@
         <v>266</v>
       </c>
       <c r="D210" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4894,7 +4903,7 @@
         <v>266</v>
       </c>
       <c r="D211" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4908,7 +4917,7 @@
         <v>266</v>
       </c>
       <c r="D212" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4922,7 +4931,7 @@
         <v>264</v>
       </c>
       <c r="D213" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4936,7 +4945,7 @@
         <v>264</v>
       </c>
       <c r="D214" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4950,7 +4959,7 @@
         <v>264</v>
       </c>
       <c r="D215" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4964,7 +4973,7 @@
         <v>264</v>
       </c>
       <c r="D216" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4978,7 +4987,7 @@
         <v>264</v>
       </c>
       <c r="D217" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4992,7 +5001,7 @@
         <v>264</v>
       </c>
       <c r="D218" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5006,7 +5015,7 @@
         <v>264</v>
       </c>
       <c r="D219" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5020,7 +5029,7 @@
         <v>264</v>
       </c>
       <c r="D220" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5034,7 +5043,7 @@
         <v>266</v>
       </c>
       <c r="D221" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5048,7 +5057,7 @@
         <v>266</v>
       </c>
       <c r="D222" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5062,7 +5071,7 @@
         <v>264</v>
       </c>
       <c r="D223" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5076,7 +5085,7 @@
         <v>266</v>
       </c>
       <c r="D224" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5090,7 +5099,7 @@
         <v>266</v>
       </c>
       <c r="D225" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5104,7 +5113,7 @@
         <v>266</v>
       </c>
       <c r="D226" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5118,7 +5127,7 @@
         <v>266</v>
       </c>
       <c r="D227" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5132,7 +5141,7 @@
         <v>266</v>
       </c>
       <c r="D228" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5146,7 +5155,7 @@
         <v>266</v>
       </c>
       <c r="D229" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5160,7 +5169,7 @@
         <v>266</v>
       </c>
       <c r="D230" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5174,7 +5183,7 @@
         <v>266</v>
       </c>
       <c r="D231" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5188,7 +5197,7 @@
         <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5199,10 +5208,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D233" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5216,7 +5225,7 @@
         <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5230,7 +5239,7 @@
         <v>264</v>
       </c>
       <c r="D235" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5244,7 +5253,7 @@
         <v>264</v>
       </c>
       <c r="D236" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5258,7 +5267,7 @@
         <v>264</v>
       </c>
       <c r="D237" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5272,7 +5281,7 @@
         <v>264</v>
       </c>
       <c r="D238" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5286,7 +5295,7 @@
         <v>264</v>
       </c>
       <c r="D239" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5300,7 +5309,7 @@
         <v>264</v>
       </c>
       <c r="D240" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5314,7 +5323,7 @@
         <v>264</v>
       </c>
       <c r="D241" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5328,7 +5337,7 @@
         <v>264</v>
       </c>
       <c r="D242" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5342,7 +5351,7 @@
         <v>266</v>
       </c>
       <c r="D243" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5356,7 +5365,7 @@
         <v>266</v>
       </c>
       <c r="D244" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5370,7 +5379,7 @@
         <v>266</v>
       </c>
       <c r="D245" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5384,7 +5393,7 @@
         <v>266</v>
       </c>
       <c r="D246" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5398,7 +5407,7 @@
         <v>266</v>
       </c>
       <c r="D247" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5409,10 +5418,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D248" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5426,7 +5435,7 @@
         <v>266</v>
       </c>
       <c r="D249" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5440,7 +5449,7 @@
         <v>266</v>
       </c>
       <c r="D250" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5454,7 +5463,7 @@
         <v>264</v>
       </c>
       <c r="D251" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5468,7 +5477,7 @@
         <v>265</v>
       </c>
       <c r="D252" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5482,7 +5491,7 @@
         <v>265</v>
       </c>
       <c r="D253" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5496,7 +5505,7 @@
         <v>265</v>
       </c>
       <c r="D254" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5510,7 +5519,7 @@
         <v>265</v>
       </c>
       <c r="D255" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5524,7 +5533,7 @@
         <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>
